--- a/exports/FINNIFTY_full_report.xlsx
+++ b/exports/FINNIFTY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>3.72</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>18161.5</v>
+        <v>18098.95</v>
       </c>
       <c r="I2" t="n">
         <v>18112.09764460841</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.22</v>
+        <v>-1.56</v>
       </c>
       <c r="L2" t="n">
-        <v>2.17</v>
+        <v>2.86</v>
       </c>
       <c r="M2" t="n">
-        <v>0.59</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>1.08</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>2.65</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>18100.65</v>
+        <v>18362.3</v>
       </c>
       <c r="I3" t="n">
         <v>18248.50555380889</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.01</v>
+        <v>-1.46</v>
       </c>
       <c r="L3" t="n">
-        <v>0.65</v>
+        <v>1.65</v>
       </c>
       <c r="M3" t="n">
         <v>1.32</v>
       </c>
       <c r="N3" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="O3" t="n">
         <v>-0.27</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>5.1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44599.55208333334</v>
+        <v>44600.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>17602.75</v>
+        <v>17479.8</v>
       </c>
       <c r="I4" t="n">
         <v>17561.60852083448</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.14</v>
+        <v>-4.81</v>
       </c>
       <c r="L4" t="n">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="M4" t="n">
         <v>0.44</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>4.85</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>15877.3</v>
+        <v>16271.45</v>
       </c>
       <c r="I5" t="n">
         <v>16264.08382777531</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>9.17</v>
+        <v>6.91</v>
       </c>
       <c r="L5" t="n">
         <v>3.81</v>
       </c>
       <c r="M5" t="n">
-        <v>2.17</v>
+        <v>3.71</v>
       </c>
       <c r="N5" t="n">
         <v>3.42</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>6.52</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>17404.4</v>
+        <v>16973.2</v>
       </c>
       <c r="I6" t="n">
         <v>17385.54962537024</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K6" t="n">
-        <v>6.96</v>
+        <v>4.31</v>
       </c>
       <c r="L6" t="n">
         <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="O6" t="n">
         <v>1.42</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>4.55</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44706.55208333334</v>
+        <v>44707.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>15914.2</v>
+        <v>16132.6</v>
       </c>
       <c r="I7" t="n">
         <v>16100.11558918453</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K7" t="n">
-        <v>6.24</v>
+        <v>4.95</v>
       </c>
       <c r="L7" t="n">
         <v>1.17</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>4.59</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>16219.4</v>
+        <v>15879.25</v>
       </c>
       <c r="I8" t="n">
         <v>16070.33470008001</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>0.54</v>
+        <v>-1.57</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>2.26</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>3.95</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>15411.35</v>
+        <v>15623.95</v>
       </c>
       <c r="I9" t="n">
         <v>15581.90391346122</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>2.95</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>1.04</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.52</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>18082.6</v>
+        <v>17803</v>
       </c>
       <c r="I10" t="n">
         <v>17957.64571302663</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K10" t="n">
-        <v>15.74</v>
+        <v>13.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.97</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>3.42</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44803.38541666666</v>
+        <v>44803.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>18018</v>
+        <v>18225.6</v>
       </c>
       <c r="I11" t="n">
         <v>18212.24423794661</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.21</v>
+        <v>-2.37</v>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
         <v>0.73</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.04</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>18405.2</v>
+        <v>17970</v>
       </c>
       <c r="I12" t="n">
         <v>18263.56040610347</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>0.99</v>
+        <v>-1.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.71</v>
@@ -1125,7 +1268,7 @@
         <v>1.71</v>
       </c>
       <c r="N12" t="n">
-        <v>1.39</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
         <v>3.16</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.81</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>17745.05</v>
+        <v>17868.3</v>
       </c>
       <c r="I13" t="n">
         <v>17866.63667994906</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>1.25</v>
+        <v>0.57</v>
       </c>
       <c r="L13" t="n">
         <v>2.06</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.37</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>19163.25</v>
+        <v>19111.05</v>
       </c>
       <c r="I14" t="n">
         <v>19151.25517480707</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>71</v>
+        <v>71.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>7.25</v>
+        <v>6.96</v>
       </c>
       <c r="L14" t="n">
         <v>3.09</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>2.04</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44924.38541666666</v>
+        <v>44924.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>18908.85</v>
+        <v>19111.35</v>
       </c>
       <c r="I15" t="n">
         <v>19109.43596639396</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>1.06</v>
+        <v>-0</v>
       </c>
       <c r="L15" t="n">
         <v>1.13</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>3.21</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44931.55208333334</v>
+        <v>44932.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>18786.55</v>
+        <v>18556.35</v>
       </c>
       <c r="I16" t="n">
         <v>18730.80799195534</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.7</v>
+        <v>-2.9</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="M16" t="n">
         <v>0.27</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>3.54</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44971.38541666666</v>
+        <v>44971.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>18523</v>
+        <v>18586.1</v>
       </c>
       <c r="I17" t="n">
         <v>18561.06745343116</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="L17" t="n">
         <v>2.41</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>2.77</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>18277.85</v>
+        <v>18003</v>
       </c>
       <c r="I18" t="n">
         <v>18203.81961824938</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.66</v>
+        <v>-3.14</v>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>3.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.02</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
         <v>0.91</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>3.28</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>18258.65</v>
+        <v>18409.6</v>
       </c>
       <c r="I19" t="n">
         <v>18348.85823913334</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.42</v>
+        <v>-2.26</v>
       </c>
       <c r="L19" t="n">
-        <v>1.78</v>
+        <v>2.57</v>
       </c>
       <c r="M19" t="n">
         <v>0.75</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>2.57</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44994.55208333334</v>
+        <v>44995.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>18243.25</v>
+        <v>17952.75</v>
       </c>
       <c r="I20" t="n">
         <v>17976.62735835814</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9</v>
+        <v>-2.48</v>
       </c>
       <c r="L20" t="n">
-        <v>0.93</v>
+        <v>2.96</v>
       </c>
       <c r="M20" t="n">
-        <v>0.35</v>
+        <v>0.91</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
         <v>0.67</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>2.82</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>17831.7</v>
+        <v>17999.7</v>
       </c>
       <c r="I21" t="n">
         <v>17972.96836179707</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>0.67</v>
+        <v>-0.26</v>
       </c>
       <c r="L21" t="n">
         <v>0.7</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.02</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45051.38541666666</v>
+        <v>45051.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>19184.2</v>
+        <v>19019.65</v>
       </c>
       <c r="I22" t="n">
         <v>19047.79284259532</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>6.58</v>
+        <v>5.67</v>
       </c>
       <c r="L22" t="n">
         <v>0.47</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>2.8</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45058.55208333334</v>
+        <v>45061.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>19509.4</v>
+        <v>19596.35</v>
       </c>
       <c r="I23" t="n">
         <v>19552.55029749779</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.57</v>
+        <v>-3.03</v>
       </c>
       <c r="L23" t="n">
-        <v>2.82</v>
+        <v>3.09</v>
       </c>
       <c r="M23" t="n">
         <v>0.48</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>2.44</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45070.55208333334</v>
+        <v>45071.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>19241.25</v>
+        <v>19146.5</v>
       </c>
       <c r="I24" t="n">
         <v>19202.84631789728</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.81</v>
+        <v>-2.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="M24" t="n">
         <v>0.29</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>2.22</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45076.38541666666</v>
+        <v>45076.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>19524.8</v>
+        <v>19623.9</v>
       </c>
       <c r="I25" t="n">
         <v>19568.59769494694</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.98</v>
+        <v>-2.49</v>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="M25" t="n">
         <v>0.78</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>2.15</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45118.38541666666</v>
+        <v>45118.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>20152.7</v>
+        <v>19988.7</v>
       </c>
       <c r="I26" t="n">
         <v>20041.95974223566</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>2.69</v>
+        <v>1.86</v>
       </c>
       <c r="L26" t="n">
         <v>2.08</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>2.41</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45126.38541666666</v>
+        <v>45126.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>20351.15</v>
+        <v>20377.85</v>
       </c>
       <c r="I27" t="n">
         <v>20377.05106109287</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.81</v>
+        <v>-1.95</v>
       </c>
       <c r="L27" t="n">
         <v>2.44</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>2.31</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>20323.45</v>
+        <v>20067.4</v>
       </c>
       <c r="I28" t="n">
         <v>20131.39840979095</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.27</v>
+        <v>-1.52</v>
       </c>
       <c r="L28" t="n">
-        <v>0.89</v>
+        <v>1.53</v>
       </c>
       <c r="M28" t="n">
-        <v>0.41</v>
+        <v>0.74</v>
       </c>
       <c r="N28" t="n">
-        <v>0.65</v>
+        <v>1.28</v>
       </c>
       <c r="O28" t="n">
         <v>0.57</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>2.59</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>19805.7</v>
+        <v>19864.15</v>
       </c>
       <c r="I29" t="n">
         <v>19849.33222628729</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="L29" t="n">
         <v>0.89</v>
       </c>
       <c r="M29" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="N29" t="n">
         <v>1.04</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>1.55</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45187.55208333334</v>
+        <v>45189.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>20403.85</v>
+        <v>20132.3</v>
       </c>
       <c r="I30" t="n">
         <v>20140.03745593407</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>2.72</v>
+        <v>1.35</v>
       </c>
       <c r="L30" t="n">
         <v>1.6</v>
       </c>
       <c r="M30" t="n">
-        <v>0.14</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0.57</v>
+        <v>1.37</v>
       </c>
       <c r="O30" t="n">
         <v>-0.57</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>2.32</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>19822.7</v>
+        <v>19963.15</v>
       </c>
       <c r="I31" t="n">
         <v>19951.2857870693</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n">
-        <v>1.54</v>
+        <v>0.84</v>
       </c>
       <c r="L31" t="n">
         <v>0.67</v>
       </c>
       <c r="M31" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="N31" t="n">
         <v>1.26</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>1.77</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45218.38541666666</v>
+        <v>45218.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>19662.05</v>
+        <v>19604.9</v>
       </c>
       <c r="I32" t="n">
         <v>19619.1020416963</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.51</v>
+        <v>-1.79</v>
       </c>
       <c r="L32" t="n">
         <v>2.32</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>2.27</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>19279.7</v>
+        <v>19393.1</v>
       </c>
       <c r="I33" t="n">
         <v>19385.98020501535</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="L33" t="n">
         <v>0.67</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>2.23</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45307.55208333334</v>
+        <v>45308.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>21439.75</v>
+        <v>20648.2</v>
       </c>
       <c r="I34" t="n">
         <v>21100.18616747369</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>74.16666666666667</v>
+        <v>75</v>
       </c>
       <c r="K34" t="n">
-        <v>10.55</v>
+        <v>6.47</v>
       </c>
       <c r="L34" t="n">
         <v>0.19</v>
       </c>
       <c r="M34" t="n">
-        <v>1.13</v>
+        <v>3.29</v>
       </c>
       <c r="N34" t="n">
-        <v>1.51</v>
+        <v>4.16</v>
       </c>
       <c r="O34" t="n">
         <v>0.43</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>3.76</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45338.55208333334</v>
+        <v>45341.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>20456.95</v>
+        <v>20598.7</v>
       </c>
       <c r="I35" t="n">
         <v>20526.4979700355</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K35" t="n">
-        <v>0.93</v>
+        <v>0.24</v>
       </c>
       <c r="L35" t="n">
         <v>1.78</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>3.09</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>21484.35</v>
+        <v>21252.9</v>
       </c>
       <c r="I36" t="n">
         <v>21345.48354730866</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K36" t="n">
-        <v>4.3</v>
+        <v>3.18</v>
       </c>
       <c r="L36" t="n">
         <v>1.77</v>
       </c>
       <c r="M36" t="n">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="N36" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="O36" t="n">
         <v>0.47</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>2.14</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45405.55208333334</v>
+        <v>45406.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>21318.6</v>
+        <v>21452.8</v>
       </c>
       <c r="I37" t="n">
         <v>21381.06254473285</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.31</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="M37" t="n">
         <v>1.03</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>2.44</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>21455.35</v>
+        <v>21189</v>
       </c>
       <c r="I38" t="n">
         <v>21369.39294929152</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>0.01</v>
+        <v>-1.23</v>
       </c>
       <c r="L38" t="n">
-        <v>0.85</v>
+        <v>1.32</v>
       </c>
       <c r="M38" t="n">
         <v>0.71</v>
       </c>
       <c r="N38" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="O38" t="n">
         <v>0.59</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>3.19</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45434.55208333334</v>
+        <v>45435.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>21370.15</v>
+        <v>21627.6</v>
       </c>
       <c r="I39" t="n">
         <v>21608.76559965634</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.85</v>
+        <v>-2.07</v>
       </c>
       <c r="L39" t="n">
-        <v>1.6</v>
+        <v>2.21</v>
       </c>
       <c r="M39" t="n">
         <v>0.51</v>
       </c>
       <c r="N39" t="n">
-        <v>0.98</v>
+        <v>1.62</v>
       </c>
       <c r="O39" t="n">
         <v>-1.6</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>3</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>22654.1</v>
+        <v>20997.25</v>
       </c>
       <c r="I40" t="n">
         <v>21792.87130349633</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>4.75</v>
+        <v>-2.91</v>
       </c>
       <c r="L40" t="n">
-        <v>1.27</v>
+        <v>5.41</v>
       </c>
       <c r="M40" t="n">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="N40" t="n">
-        <v>1.47</v>
+        <v>7.55</v>
       </c>
       <c r="O40" t="n">
         <v>1.62</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45457.55208333334</v>
+        <v>45461.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>22400.85</v>
+        <v>22521.2</v>
       </c>
       <c r="I41" t="n">
         <v>22436.71874416797</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.68</v>
+        <v>-7.26</v>
       </c>
       <c r="L41" t="n">
-        <v>7.04</v>
+        <v>7.28</v>
       </c>
       <c r="M41" t="n">
         <v>1.14</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>3.56</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>23648.95</v>
+        <v>23117.85</v>
       </c>
       <c r="I42" t="n">
         <v>23285.15525917476</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K42" t="n">
-        <v>5.01</v>
+        <v>2.65</v>
       </c>
       <c r="L42" t="n">
         <v>0.74</v>
@@ -2835,7 +3338,7 @@
         <v>0.96</v>
       </c>
       <c r="N42" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="O42" t="n">
         <v>0.87</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>3.98</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>22941.8</v>
+        <v>23221.55</v>
       </c>
       <c r="I43" t="n">
         <v>23213.54117153842</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K43" t="n">
-        <v>0.76</v>
+        <v>-0.45</v>
       </c>
       <c r="L43" t="n">
         <v>2.63</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>3.23</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>24915.5</v>
+        <v>24552</v>
       </c>
       <c r="I44" t="n">
         <v>24583.75716528404</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K44" t="n">
-        <v>7.29</v>
+        <v>5.73</v>
       </c>
       <c r="L44" t="n">
         <v>1.27</v>
@@ -2949,7 +3476,7 @@
         <v>0.54</v>
       </c>
       <c r="N44" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="O44" t="n">
         <v>0.86</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>2.85</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45593.55208333334</v>
+        <v>45594.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>23883.65</v>
+        <v>24156.7</v>
       </c>
       <c r="I45" t="n">
         <v>24120.69399991379</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K45" t="n">
-        <v>2.72</v>
+        <v>1.61</v>
       </c>
       <c r="L45" t="n">
         <v>1.22</v>
@@ -3006,7 +3545,7 @@
         <v>0.55</v>
       </c>
       <c r="N45" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="O45" t="n">
         <v>-1.73</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>3.65</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>23551.4</v>
+        <v>23371.05</v>
       </c>
       <c r="I46" t="n">
         <v>23512.23686430728</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.51</v>
+        <v>-3.25</v>
       </c>
       <c r="L46" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="M46" t="n">
         <v>0.54</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>3.77</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>23606.25</v>
+        <v>23991.6</v>
       </c>
       <c r="I47" t="n">
         <v>23930.74938214133</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.01</v>
+        <v>-2.66</v>
       </c>
       <c r="L47" t="n">
-        <v>1.29</v>
+        <v>3.27</v>
       </c>
       <c r="M47" t="n">
-        <v>0.45</v>
+        <v>1.83</v>
       </c>
       <c r="N47" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="O47" t="n">
         <v>-1.4</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>2.93</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>24476.2</v>
+        <v>24243.95</v>
       </c>
       <c r="I48" t="n">
         <v>24292.54949306279</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K48" t="n">
-        <v>2.02</v>
+        <v>1.05</v>
       </c>
       <c r="L48" t="n">
         <v>0.58</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>2.97</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45686.38541666666</v>
+        <v>45686.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>22979.4</v>
+        <v>23036.45</v>
       </c>
       <c r="I49" t="n">
         <v>23010.74812156254</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>5.22</v>
+        <v>4.98</v>
       </c>
       <c r="L49" t="n">
         <v>1.11</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>3.05</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45709.55208333334</v>
+        <v>45712.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>23135.2</v>
+        <v>22967.45</v>
       </c>
       <c r="I50" t="n">
         <v>23009.01872739577</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>0.43</v>
+        <v>-0.3</v>
       </c>
       <c r="L50" t="n">
         <v>1.04</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>2.69</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45729.55208333334</v>
+        <v>45733.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>23273.05</v>
+        <v>23514.75</v>
       </c>
       <c r="I51" t="n">
         <v>23502.96185993446</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.33</v>
+        <v>-2.38</v>
       </c>
       <c r="L51" t="n">
-        <v>2.14</v>
+        <v>2.59</v>
       </c>
       <c r="M51" t="n">
         <v>0.52</v>
       </c>
       <c r="N51" t="n">
-        <v>0.83</v>
+        <v>1.13</v>
       </c>
       <c r="O51" t="n">
         <v>-0.6</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>2.44</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45748.38541666666</v>
+        <v>45748.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>24578.25</v>
+        <v>24541.25</v>
       </c>
       <c r="I52" t="n">
         <v>24560.05296336862</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>4.52</v>
+        <v>4.37</v>
       </c>
       <c r="L52" t="n">
         <v>0.89</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>2.66</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>24549.4</v>
+        <v>25252.3</v>
       </c>
       <c r="I53" t="n">
         <v>24730.77105370735</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.03</v>
+        <v>-2.9</v>
       </c>
       <c r="L53" t="n">
-        <v>1.64</v>
+        <v>3.06</v>
       </c>
       <c r="M53" t="n">
-        <v>0.71</v>
+        <v>2.71</v>
       </c>
       <c r="N53" t="n">
-        <v>1.61</v>
+        <v>3.06</v>
       </c>
       <c r="O53" t="n">
         <v>-2.05</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>4.44</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>25869.5</v>
+        <v>25512.5</v>
       </c>
       <c r="I54" t="n">
         <v>25779.5931139016</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="L54" t="n">
         <v>0.86</v>
       </c>
       <c r="M54" t="n">
-        <v>0.29</v>
+        <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="O54" t="n">
         <v>3.06</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>3.49</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>25547.6</v>
+        <v>26387</v>
       </c>
       <c r="I55" t="n">
         <v>26201.63628737127</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.14</v>
+        <v>-3.43</v>
       </c>
       <c r="L55" t="n">
-        <v>1.17</v>
+        <v>3.7</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O55" t="n">
         <v>-1.24</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>4.11</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>26545.9</v>
+        <v>26291.6</v>
       </c>
       <c r="I56" t="n">
         <v>26411.97237462572</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6</v>
+        <v>-0.36</v>
       </c>
       <c r="L56" t="n">
         <v>1.63</v>
       </c>
       <c r="M56" t="n">
-        <v>0.35</v>
+        <v>1.56</v>
       </c>
       <c r="N56" t="n">
         <v>1.05</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>2.1</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>26541.9</v>
+        <v>26831.3</v>
       </c>
       <c r="I57" t="n">
         <v>26810.93841486636</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.95</v>
+        <v>-2.05</v>
       </c>
       <c r="L57" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="M57" t="n">
-        <v>0.15</v>
+        <v>0.91</v>
       </c>
       <c r="N57" t="n">
         <v>1.38</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>2.17</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45841.38541666666</v>
+        <v>45841.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>26847.85</v>
+        <v>26731.15</v>
       </c>
       <c r="I58" t="n">
         <v>26747.70355105391</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>0.06</v>
+        <v>-0.37</v>
       </c>
       <c r="L58" t="n">
         <v>0.57</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>2.29</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45859.55208333334</v>
+        <v>45860.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>26981.35</v>
+        <v>27035.7</v>
       </c>
       <c r="I59" t="n">
         <v>27019.34494299476</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.14</v>
       </c>
       <c r="L59" t="n">
         <v>1.56</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>1.82</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>26796.8</v>
+        <v>26659.85</v>
       </c>
       <c r="I60" t="n">
         <v>26708.66668209992</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.88</v>
+        <v>-1.39</v>
       </c>
       <c r="L60" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="M60" t="n">
-        <v>0.14</v>
+        <v>0.42</v>
       </c>
       <c r="N60" t="n">
         <v>0.87</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>2.27</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>25881.85</v>
+        <v>26032.25</v>
       </c>
       <c r="I61" t="n">
         <v>26029.96271070684</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K61" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="L61" t="n">
         <v>0.74</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>2.39</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>26374.3</v>
+        <v>26244.7</v>
       </c>
       <c r="I62" t="n">
         <v>26261.6080141981</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="L62" t="n">
         <v>0.67</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>1.91</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>26439.4</v>
+        <v>26704.85</v>
       </c>
       <c r="I63" t="n">
         <v>26464.46342353187</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.74</v>
+        <v>-1.75</v>
       </c>
       <c r="L63" t="n">
-        <v>0.74</v>
+        <v>1.8</v>
       </c>
       <c r="M63" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="N63" t="n">
         <v>1.37</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>2.3</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>27181.2</v>
+        <v>27117.85</v>
       </c>
       <c r="I64" t="n">
         <v>27131.2665098275</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K64" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="L64" t="n">
         <v>0.8100000000000001</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>1.85</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45975.55208333334</v>
+        <v>45978.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>27491.9</v>
+        <v>27629.7</v>
       </c>
       <c r="I65" t="n">
         <v>27569.87191093832</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.38</v>
+        <v>-1.89</v>
       </c>
       <c r="L65" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="M65" t="n">
         <v>0.66</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>2.15</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46007.38541666666</v>
+        <v>46007.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>27415.8</v>
+        <v>27374.2</v>
       </c>
       <c r="I66" t="n">
         <v>27404.08744580006</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.77</v>
+        <v>-0.92</v>
       </c>
       <c r="L66" t="n">
         <v>1.02</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>1.81</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>27671.15</v>
+        <v>27897.6</v>
       </c>
       <c r="I67" t="n">
         <v>27694.02369543368</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.08</v>
+        <v>-1.91</v>
       </c>
       <c r="L67" t="n">
-        <v>1.27</v>
+        <v>2.02</v>
       </c>
       <c r="M67" t="n">
         <v>0.31</v>
       </c>
       <c r="N67" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="O67" t="n">
         <v>-0.77</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>1.92</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>27662.6</v>
+        <v>27397.8</v>
       </c>
       <c r="I68" t="n">
         <v>27503.77283599014</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.84</v>
+        <v>-1.79</v>
       </c>
       <c r="L68" t="n">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="M68" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="N68" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O68" t="n">
         <v>0.86</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>2.28</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46051.38541666666</v>
+        <v>46051.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>27456</v>
+        <v>27530.55</v>
       </c>
       <c r="I69" t="n">
         <v>27515.21887597684</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.21</v>
+        <v>-0.48</v>
       </c>
       <c r="L69" t="n">
         <v>1.19</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>2.59</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46054.38541666666</v>
+        <v>46054.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>26960.25</v>
+        <v>26698.25</v>
       </c>
       <c r="I70" t="n">
         <v>26816.36333867443</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.07</v>
+        <v>-3.02</v>
       </c>
       <c r="L70" t="n">
         <v>4.22</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>3.85</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>26812.75</v>
+        <v>27735.3</v>
       </c>
       <c r="I71" t="n">
         <v>27558.52797814613</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.43</v>
+        <v>-3.88</v>
       </c>
       <c r="L71" t="n">
-        <v>1.03</v>
+        <v>5.91</v>
       </c>
       <c r="M71" t="n">
-        <v>0.01</v>
+        <v>4.9</v>
       </c>
       <c r="N71" t="n">
-        <v>0.43</v>
+        <v>3.12</v>
       </c>
       <c r="O71" t="n">
         <v>-2.27</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,25 +5387,25 @@
         <v>3.96</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>27872.6</v>
+        <v>27405.5</v>
       </c>
       <c r="I72" t="n">
         <v>27846.40940575877</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5</v>
+        <v>-1.19</v>
       </c>
       <c r="L72" t="n">
-        <v>0.74</v>
+        <v>1.46</v>
       </c>
       <c r="M72" t="n">
-        <v>0.63</v>
+        <v>1.86</v>
       </c>
       <c r="N72" t="n">
         <v>1.46</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>3.09</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>24663.4</v>
+        <v>26017.55</v>
       </c>
       <c r="I73" t="n">
         <v>24855.61497868263</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K73" t="n">
-        <v>10.01</v>
+        <v>5.06</v>
       </c>
       <c r="L73" t="n">
         <v>1.11</v>
       </c>
       <c r="M73" t="n">
-        <v>2.35</v>
+        <v>4.16</v>
       </c>
       <c r="N73" t="n">
-        <v>2.51</v>
+        <v>5.76</v>
       </c>
       <c r="O73" t="n">
         <v>-1.18</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>6.55</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46140.38541666666</v>
+        <v>46140.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>26001.15</v>
+        <v>25912.25</v>
       </c>
       <c r="I74" t="n">
         <v>25962.6748708586</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="L74" t="n">
         <v>1.89</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>2.89</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46148.38541666666</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="H75" t="n">
-        <v>25872.95</v>
+        <v>26432.45</v>
       </c>
       <c r="I75" t="n">
         <v>26393.93237964981</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K75" t="n">
-        <v>0.15</v>
+        <v>-2.01</v>
       </c>
       <c r="L75" t="n">
-        <v>0.95</v>
+        <v>2.08</v>
       </c>
       <c r="M75" t="n">
         <v>0.82</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>4.26</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46153.38541666666</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>25850.9</v>
+        <v>25655.95</v>
       </c>
       <c r="I76" t="n">
         <v>25662.83663836598</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.2</v>
+        <v>-2.94</v>
       </c>
       <c r="L76" t="n">
         <v>3.22</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>3.73</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>25566.25</v>
+        <v>26012.4</v>
       </c>
       <c r="I77" t="n">
         <v>25951.40865709547</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K77" t="n">
-        <v>0.35</v>
+        <v>-1.39</v>
       </c>
       <c r="L77" t="n">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="M77" t="n">
-        <v>0.74</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N77" t="n">
-        <v>1.47</v>
+        <v>2.25</v>
       </c>
       <c r="O77" t="n">
         <v>-1.36</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>3.66</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>25428.45</v>
+        <v>25052.85</v>
       </c>
       <c r="I78" t="n">
         <v>25274.55572147327</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.24</v>
+        <v>-3.69</v>
       </c>
       <c r="L78" t="n">
-        <v>2.78</v>
+        <v>3.73</v>
       </c>
       <c r="M78" t="n">
         <v>0.51</v>
       </c>
       <c r="N78" t="n">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
       <c r="O78" t="n">
         <v>2.25</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>4.04</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46184.55208333334</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>25176</v>
+        <v>25486.3</v>
       </c>
       <c r="I79" t="n">
         <v>25483.0956459294</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.49</v>
+        <v>-1.73</v>
       </c>
       <c r="L79" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="M79" t="n">
-        <v>0.64</v>
+        <v>1.24</v>
       </c>
       <c r="N79" t="n">
-        <v>1.57</v>
+        <v>3.05</v>
       </c>
       <c r="O79" t="n">
         <v>-1.64</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>3.22</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H80" t="n">
-        <v>26780.3</v>
+        <v>26348.1</v>
       </c>
       <c r="I80" t="n">
         <v>26514.6808974247</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K80" t="n">
-        <v>5.08</v>
+        <v>3.38</v>
       </c>
       <c r="L80" t="n">
         <v>0.33</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>3.11</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>26233.55</v>
+        <v>26588.4</v>
       </c>
       <c r="I81" t="n">
         <v>26497.20953759702</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K81" t="n">
-        <v>0.43</v>
+        <v>-0.91</v>
       </c>
       <c r="L81" t="n">
         <v>2.32</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>2.68</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H82" t="n">
-        <v>26432.4</v>
+        <v>26290.2</v>
       </c>
       <c r="I82" t="n">
         <v>26298.02636018116</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.59</v>
+        <v>-1.12</v>
       </c>
       <c r="L82" t="n">
-        <v>0.99</v>
+        <v>1.27</v>
       </c>
       <c r="M82" t="n">
         <v>0.6</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>2.31</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H83" t="n">
-        <v>24985.75</v>
+        <v>25228.55</v>
       </c>
       <c r="I83" t="n">
         <v>25132.38969571919</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K83" t="n">
-        <v>4.96</v>
+        <v>4.04</v>
       </c>
       <c r="L83" t="n">
         <v>0.78</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>3</v>
+      </c>
+      <c r="U83" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -5208,22 +6215,22 @@
         <v>3.22</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H84" t="n">
-        <v>24987.1</v>
+        <v>24602.1</v>
       </c>
       <c r="I84" t="n">
         <v>24665.28553735622</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.96</v>
+        <v>-2.48</v>
       </c>
       <c r="L84" t="n">
-        <v>1.36</v>
+        <v>2.49</v>
       </c>
       <c r="M84" t="n">
         <v>0.21</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5289,6 +6308,12 @@
       <c r="Q85" t="n">
         <v>10</v>
       </c>
+      <c r="R85" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7391,7 +8416,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -7401,7 +8426,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -7411,7 +8436,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -7421,7 +8446,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -7431,7 +8456,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.7</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="10">
@@ -7441,7 +8466,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.8</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="11">
@@ -7451,7 +8476,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -7461,7 +8486,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -7471,7 +8496,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79.5</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="14">
@@ -7481,7 +8506,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.16</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="15">
@@ -7491,7 +8516,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.61</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="16">
@@ -7501,7 +8526,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="17">
@@ -7511,7 +8536,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.74</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="18">
@@ -7521,7 +8546,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="19">
@@ -7531,7 +8556,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="20">
@@ -7541,7 +8566,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21">
@@ -7551,7 +8576,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.04</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="22">
@@ -7561,7 +8586,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -7581,7 +8606,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.73</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="25">
@@ -7591,7 +8616,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.35</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="26">
@@ -7601,7 +8626,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="27">
@@ -7611,7 +8636,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.42</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="28">
@@ -7621,7 +8646,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
